--- a/XlsxSharp.Tests/Resource/Examples/Misc/DataTypes.xlsx
+++ b/XlsxSharp.Tests/Resource/Examples/Misc/DataTypes.xlsx
@@ -1,93 +1,93 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Data Types" sheetId="1" r:id="rId2"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Data Types" sheetId="1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="125725"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>Plain Text:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hello World.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plain Date:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plain DateTime:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plain Boolean:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Plain Number:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TimeSpan:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Large Double Number:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Explicit Text:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Date as Text:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9/2/2010 12:00:00 AM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DateTime as Text:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9/2/2010 1:45:22 PM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Boolean as Text:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Number as Text:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123.45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Number with @ format:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Format number with @:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TimeSpan as Text:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.09:45:22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Inline String:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Error from literal:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Error from evaluation:</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>Plain Text:</t>
+  </si>
+  <si>
+    <t>Hello World.</t>
+  </si>
+  <si>
+    <t>Plain Date:</t>
+  </si>
+  <si>
+    <t>Plain DateTime:</t>
+  </si>
+  <si>
+    <t>Plain Boolean:</t>
+  </si>
+  <si>
+    <t>Plain Number:</t>
+  </si>
+  <si>
+    <t>TimeSpan:</t>
+  </si>
+  <si>
+    <t>Large Double Number:</t>
+  </si>
+  <si>
+    <t>Explicit Text:</t>
+  </si>
+  <si>
+    <t>Date as Text:</t>
+  </si>
+  <si>
+    <t>9/2/2010 12:00:00 AM</t>
+  </si>
+  <si>
+    <t>DateTime as Text:</t>
+  </si>
+  <si>
+    <t>9/2/2010 1:45:22 PM</t>
+  </si>
+  <si>
+    <t>Boolean as Text:</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>Number as Text:</t>
+  </si>
+  <si>
+    <t>123.45</t>
+  </si>
+  <si>
+    <t>Number with @ format:</t>
+  </si>
+  <si>
+    <t>Format number with @:</t>
+  </si>
+  <si>
+    <t>TimeSpan as Text:</t>
+  </si>
+  <si>
+    <t>1.09:45:22</t>
+  </si>
+  <si>
+    <t>Inline String:</t>
+  </si>
+  <si>
+    <t>Error from literal:</t>
+  </si>
+  <si>
+    <t>Error from evaluation:</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,169 +428,169 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:C22"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20.567768" style="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="2" spans="1:3">
-      <x:c r="B2" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="B3" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="1">
-        <x:v>40423</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="B4" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="2">
-        <x:v>40423.5731712963</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:3">
-      <x:c r="B5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:3">
-      <x:c r="B6" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>123.45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:3">
-      <x:c r="B7" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="3">
-        <x:v>1.40650462962963</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:3">
-      <x:c r="B9" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>9.999E+307</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:3">
-      <x:c r="B11" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="4" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:3">
-      <x:c r="B12" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" s="4" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:3">
-      <x:c r="B13" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C13" s="4" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:3">
-      <x:c r="B14" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="4" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:3">
-      <x:c r="B15" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="4" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:3">
-      <x:c r="B16" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C16" s="5">
-        <x:v>123.45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:3">
-      <x:c r="B17" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C17" s="5">
-        <x:v>123.45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:3">
-      <x:c r="B18" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C18" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:3">
-      <x:c r="B19" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="inlineStr">
-        <x:is>
-          <x:t>Not Shared</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:3">
-      <x:c r="B21" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="e">
-        <x:v>#VALUE!</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="B22" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C22" s="0">
-        <x:f>1/0</x:f>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" style="0" customWidth="1" width="9.140625"/>
+    <col min="2" max="2" style="0" customWidth="1" width="22.710625"/>
+    <col min="3" max="3" style="0" customWidth="1" width="20.567768"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3">
+      <c r="B2" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="B3" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>40423</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="B4" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>40423.5731712963</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="0">
+        <v>123.45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.40650462962963</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="0">
+        <v>9.999E+307</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="B13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="B16" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="5">
+        <v>123.45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="B17" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="5">
+        <v>123.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="B18" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="B19" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Not Shared</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="B21" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="0" t="e">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="B22" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="0">
+        <f>1/0</f>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>